--- a/hiring_companies_2026-10-22.xlsx
+++ b/hiring_companies_2026-10-22.xlsx
@@ -413,17 +413,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -439,30 +440,35 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Remote?</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Roles hiring</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Job link</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Posted</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>LinkedIn note</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Verification</t>
         </is>
@@ -471,7 +477,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NetEase Games</t>
+          <t>SMT INC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,30 +487,35 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Character Performance Animator | FPS 1P View Gameplay Animator | Senior/Lead Gameplay Animator - 3C &amp; FPS</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5615277640688549509</t>
+          <t>APPLICATIONS ENGINEER I</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/-6852289303900100379</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=NetEase+Games</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=SMT+INC</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -513,7 +524,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Decisionpoint Corporation</t>
+          <t>SMT INC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,30 +534,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>System Administrator - Senior</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3948551427289468350</t>
+          <t>APPLICATIONS ENGINEER I</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/-6852289303900100379</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Decisionpoint+Corporation</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=SMT+INC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -555,7 +571,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>SMT INC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -565,30 +581,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FC Instructional Designer</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-6019371488077036857</t>
+          <t>APPLICATIONS ENGINEER I</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/-6852289303900100379</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Chewy</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=SMT+INC</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -597,7 +618,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NetEase Games</t>
+          <t>SMT INC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -607,30 +628,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Senior/Lead Gameplay Animator - 3C &amp; FPS</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/1868649066931187187</t>
+          <t>APPLICATIONS ENGINEER I</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/-6852289303900100379</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=NetEase+Games</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=SMT+INC</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -639,7 +665,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mawave</t>
+          <t>SMT INC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -649,30 +675,35 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Freelancer</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/1408229656725296522</t>
+          <t>APPLICATIONS ENGINEER I</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/-6852289303900100379</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Mawave</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=SMT+INC</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -681,7 +712,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Milton Hershey School</t>
+          <t>SMT INC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -691,30 +722,35 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PA Specialist</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2490619785498672087</t>
+          <t>APPLICATIONS ENGINEER I</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/-6852289303900100379</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Milton+Hershey+School</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=SMT+INC</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -723,82 +759,92 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Askable</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Remote (Worldwide)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Commercial Mid-Market Account Manager | Sales Director - Enterprise | Sales Ops Program Mgr | Snr Director - Enterprise Sales</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2633427836882023467</t>
+          <t>Software Engineer, AI Coding Tasks</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://remotive.com/remote-jobs/software-development/software-engineer-ai-coding-tasks-2091158</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=NetApp</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Askable</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>job link unknown</t>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>job link live</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Hologic</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DevOps Engineering Lead / Active Secret | Drone Training Coordinator / Active Secret | Network DevOps Developer - Ansible | Sr. Network Unified Communication Engineer</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-6590767951638299684</t>
+          <t>Medical Device Digital Project Engineer</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>https://jooble.org/jdp/3154306875329844457</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Peraton</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hologic</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -807,40 +853,45 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Hologic</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AI &amp; Technology Communications Manager - Tax | Applied AI Platform Engineer III | Applied AI Software Engineer III | Azure Cloud Engineer | Client Relationship Executive - St of TN (Sales Vice Preside</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/81902268409081173</t>
+          <t>Medical Device Digital Project Engineer</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/3154306875329844457</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Deloitte</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hologic</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -849,40 +900,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Hologic</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Director AI Solutions, EMEA-LATAM | Migration &amp; Modernization Business Development Manager</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1491035539003091721</t>
+          <t>Medical Device Digital Project Engineer</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/3154306875329844457</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=NetApp</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hologic</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -891,40 +947,45 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Diingu</t>
+          <t>Hologic</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote E-Learning-Autor: Pflegekinderhilfe Curricula</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4257866499279746318</t>
+          <t>Medical Device Digital Project Engineer</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/3154306875329844457</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Diingu</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hologic</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -933,40 +994,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NetEase Games</t>
+          <t>Hologic</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Character Performance Animator | FPS 1P View Gameplay Animator | Senior/Lead Gameplay Animator - 3C &amp; FPS</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-6542308456245372489</t>
+          <t>Medical Device Digital Project Engineer</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/3154306875329844457</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=NetEase+Games</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hologic</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -975,40 +1041,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Reach plc</t>
+          <t>Hologic</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Video Producer, WalesOnline</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2728648905444359009</t>
+          <t>Medical Device Digital Project Engineer</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>https://jooble.org/jdp/3154306875329844457</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Reach+plc</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hologic</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1017,82 +1088,92 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bybit</t>
+          <t>Mitre Media</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Remote (Worldwide)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Global Community Manager | Global Talent Acquisition Lead/ Expert | RWA Product Manager | Senior Data Engineer | Senior HRBP Specialist, Technology &amp; Engineering | Senior User Reach &amp; Lifecycle Manage</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-9030425484701261947</t>
+          <t>Tech Lead Full-Stack Rails Engineer</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>https://remotive.com/remote-jobs/software-development/tech-lead-full-stack-rails-engineer-2069746</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Bybit</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Mitre+Media</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>job link unknown</t>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>job link live</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cracker Barrel</t>
+          <t>Neighborly</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Allocation and Replenish Analyst | Analytics Engineer | Ecommerce Analyst | Workers Compensation Specialist</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4542991738346895029</t>
+          <t>Local Performance Marketing Specialist</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/6585664851088034080</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Cracker+Barrel</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Neighborly</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1101,40 +1182,45 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Verkor</t>
+          <t>Neighborly</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>APG Leader Maintenance en Gigafactory (H/F) | APG Leader Production (H/F) | Manager Qualité UAP H/F</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8851154478692154091</t>
+          <t>Local Performance Marketing Specialist</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>https://jooble.org/jdp/6585664851088034080</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Verkor</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Neighborly</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1143,40 +1229,45 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>Neighborly</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Grocery Delivery Driver</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8993932192435711135</t>
+          <t>Local Performance Marketing Specialist</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/6585664851088034080</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Instacart</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Neighborly</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1185,40 +1276,45 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Highlight</t>
+          <t>Neighborly</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Product Designer</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4459769669848371583</t>
+          <t>Local Performance Marketing Specialist</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/6585664851088034080</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Highlight</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Neighborly</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1227,40 +1323,45 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Elliptic</t>
+          <t>Neighborly</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Marketing Operations Associate</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/1738579786220928211</t>
+          <t>Local Performance Marketing Specialist</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>https://jooble.org/jdp/6585664851088034080</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Elliptic</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Neighborly</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1269,40 +1370,45 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bakkt</t>
+          <t>Neighborly</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Senior Product Manager, OTC Trading</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5642589321419923117</t>
+          <t>Local Performance Marketing Specialist</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>https://jooble.org/jdp/6585664851088034080</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Bakkt</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Neighborly</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1311,82 +1417,92 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Wunderman Thompson</t>
+          <t>Coalition Technologies</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Remote (Worldwide)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>English Copywriter | Senior UI/UX Designer | UI/UX Motion Designer</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8919645584861744724</t>
+          <t>Remote Office Assistant</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://remotive.com/remote-jobs/marketing/remote-office-assistant-1680495</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Wunderman+Thompson</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Coalition+Technologies</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>job link unknown</t>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>job link live</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>Inovalon</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Security Engineer Junior - GRC | Security Engineer Senior - GRC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-3705493030696989347</t>
+          <t>Senior Web Developer/Designer</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>https://jooble.org/jdp/6755910780235264643</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Alan</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Inovalon</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1395,40 +1511,45 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>(unknown company)</t>
+          <t>Inovalon</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3946191913198325122</t>
+          <t>Senior Web Developer/Designer</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>https://jooble.org/jdp/6755910780235264643</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=%28unknown+company%29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Inovalon</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1437,40 +1558,45 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Guidance &amp; Assistance</t>
+          <t>Inovalon</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IMA Project Manager | Python Engineer</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3569552674842971623</t>
+          <t>Senior Web Developer/Designer</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/6755910780235264643</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Software+Guidance+%26+Assistance</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Inovalon</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1479,40 +1605,45 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Wayve</t>
+          <t>Inovalon</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Engineering Manager, Experiment Platform, Robot Software | Software Engineer - Map &amp; Route | Staff Software Engineer, Data Enrichment Platform</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7165416180475126025</t>
+          <t>Senior Web Developer/Designer</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>https://jooble.org/jdp/6755910780235264643</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Wayve</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Inovalon</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1521,40 +1652,45 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OneBullEx</t>
+          <t>Inovalon</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Business Development Leader (Strategic Partnerships &amp; Global Sales) | Senior Batch Data Engineer (Alibaba Cloud Stack)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8797143331098506063</t>
+          <t>Senior Web Developer/Designer</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>https://jooble.org/jdp/6755910780235264643</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=OneBullEx</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Inovalon</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1563,40 +1699,45 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LeafHome</t>
+          <t>Inovalon</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Event Marketer | Field Canvassing Representative | Field Canvassing Team Lead | LF Sales Rep</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4321792266455537390</t>
+          <t>Senior Web Developer/Designer</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/6755910780235264643</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=LeafHome</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Inovalon</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1605,40 +1746,45 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Inetum</t>
+          <t>Perplexity AI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UX Designer Senior H/F</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-388330340731649924</t>
+          <t>Web Designer</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>https://jooble.org/jdp/2180896692470355487</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Inetum</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Perplexity+AI</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1647,40 +1793,45 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Agilent</t>
+          <t>Perplexity AI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4353289238307379420</t>
+          <t>Web Designer</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>https://jooble.org/jdp/2180896692470355487</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Agilent</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Perplexity+AI</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1689,40 +1840,45 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ducharme Group</t>
+          <t>Perplexity AI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Automotive Sales Rep with Social Media Duties - Cold Lake Chrysler | Sales Consultant (DM)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7115770753937567219</t>
+          <t>Web Designer</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/2180896692470355487</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Ducharme+Group</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Perplexity+AI</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1731,40 +1887,45 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ernst &amp; Young</t>
+          <t>Perplexity AI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Global Media Relations and Social Media Assistant Director</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4029933473940328608</t>
+          <t>Web Designer</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>https://jooble.org/jdp/2180896692470355487</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Ernst+%26+Young</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Perplexity+AI</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1773,40 +1934,45 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Perplexity AI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Associate Analyst, Business Administration- Launch Program 2027 - Dubai, UAE | Manager, Business Development - Digital Giant Segment | Manager, Transfer Solutions, Digital Partners</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3662948024038637399</t>
+          <t>Web Designer</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>https://jooble.org/jdp/2180896692470355487</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Mastercard</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Perplexity+AI</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1815,40 +1981,45 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Erie Home</t>
+          <t>Perplexity AI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Erie Home - Field Marketer</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8299390876749161964</t>
+          <t>Web Designer</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/2180896692470355487</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Erie+Home</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Perplexity+AI</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1857,40 +2028,45 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NEXTON</t>
+          <t>Ezead Media Group.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Product Designer Sénior H/F</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/1665888071484624650</t>
+          <t>Web Designer | $65/hr Remote</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>https://jooble.org/jdp/-2158543076247560826</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=NEXTON</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Ezead+Media+Group.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1899,40 +2075,45 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NAPA AUTO PARTS</t>
+          <t>Ezead Media Group.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NAPA Auto Parts Counter Sales</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1926572237704055143</t>
+          <t>Web Designer | $65/hr Remote</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>https://jooble.org/jdp/-2158543076247560826</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=NAPA+AUTO+PARTS</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Ezead+Media+Group.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1941,40 +2122,45 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Instacart Shoppers</t>
+          <t>The Choice, Inc.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Instacart Shopper - Delivery Driver</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2378512722068736981</t>
+          <t>UX/UI Web Designer</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/-7584532685798639502</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Instacart+Shoppers</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Choice%2C+Inc.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -1983,40 +2169,45 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lancesoft Europe</t>
+          <t>The Choice, Inc.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Global Retail Compliance Manager</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/29188457441262662</t>
+          <t>UX/UI Web Designer</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>https://jooble.org/jdp/-7584532685798639502</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Lancesoft+Europe</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Choice%2C+Inc.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -2025,40 +2216,45 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>The Choice, Inc.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seasonal Distribution Associate</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2937291499709921714</t>
+          <t>UX/UI Web Designer</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/-7584532685798639502</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=FedEx</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Choice%2C+Inc.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -2067,40 +2263,45 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Scalian</t>
+          <t>The Choice, Inc.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lead UX (F/H) - CDI - Annecy</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3972051617832928393</t>
+          <t>UX/UI Web Designer</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>https://jooble.org/jdp/-7584532685798639502</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Scalian</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Choice%2C+Inc.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -2109,40 +2310,45 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DataSite</t>
+          <t>LegalZoom.com</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Senior Paid Media Manager</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/476426128954015436</t>
+          <t>Senior Web Designer, Design Systems</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>https://jooble.org/jdp/-7361459487033159238</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=DataSite</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=LegalZoom.com</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -2151,40 +2357,45 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marketsupport Canada</t>
+          <t>LegalZoom.com</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Retail Merchandiser - Winnipeg, MB</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7688282811232746357</t>
+          <t>Senior Web Designer, Design Systems</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/-7361459487033159238</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Marketsupport+Canada</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=LegalZoom.com</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -2193,40 +2404,45 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Aptura</t>
+          <t>Ezead Media Group.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sales Operations AI Research Contributor</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/5635885635935541655</t>
+          <t>Web Designer | $65/hr Remote</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>https://jooble.org/jdp/-2158543076247560826</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Aptura</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Ezead+Media+Group.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -2235,40 +2451,45 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Aldi</t>
+          <t>Ezead Media Group.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Aldi Assistant Store Manager | Full-Time Assistant Store Manager | Retail Assistant Manager</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8887382682425565971</t>
+          <t>Web Designer | $65/hr Remote</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>https://jooble.org/jdp/-2158543076247560826</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Aldi</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Ezead+Media+Group.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -2277,40 +2498,45 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Repligen</t>
+          <t>Ezead Media Group.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pricing Manager</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6019671272937987865</t>
+          <t>Web Designer | $65/hr Remote</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>https://jooble.org/jdp/-2158543076247560826</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Repligen</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Ezead+Media+Group.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -2319,40 +2545,45 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Top.legal GmbH</t>
+          <t>Ezead Media Group.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Account Executive | Founding Marketer</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7097453524562192625</t>
+          <t>Web Designer | $65/hr Remote</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>https://jooble.org/jdp/-2158543076247560826</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Top.legal+GmbH</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Ezead+Media+Group.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -2361,40 +2592,45 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Get It Now</t>
+          <t>Vanguard College Prep</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Retail Account Manager</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/2892440044051762065</t>
+          <t>Social Media Content Coordinator (PT) - Remote</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>https://jooble.org/jdp/4783736881988227281</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Get+It+Now</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Vanguard+College+Prep</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -2403,40 +2639,45 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Repligen</t>
+          <t>Vanguard College Prep</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pricing Manager</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8282549548239525930</t>
+          <t>Social Media Content Coordinator (PT) - Remote</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>https://jooble.org/jdp/4783736881988227281</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Repligen</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Vanguard+College+Prep</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -2445,7 +2686,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jobs for Lebanon</t>
+          <t>LegalZoom.com</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2455,30 +2696,35 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sales Executive</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-306018848530965438</t>
+          <t>Senior Web Designer, Design Systems</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>https://jooble.org/jdp/-7361459487033159238</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jobs+for+Lebanon</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=LegalZoom.com</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -2487,7 +2733,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ubisoft</t>
+          <t>LegalZoom.com</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2497,30 +2743,35 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Senior Game Designer - Beyond Good &amp; Evil 2 - H/F/NB</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2446430165824908506</t>
+          <t>Senior Web Designer, Design Systems</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>https://jooble.org/jdp/-7361459487033159238</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Ubisoft</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=LegalZoom.com</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
@@ -2529,7 +2780,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ABB E-mobility</t>
+          <t>LegalZoom.com</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2539,30 +2790,35 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Key Account Manager | Key Account Manager Public Charging</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8665082665894260344</t>
+          <t>Senior Web Designer, Design Systems</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>https://jooble.org/jdp/-7361459487033159238</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=ABB+E-mobility</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>search link (open and pick the right page)</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=LegalZoom.com</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
+        <is>
+          <t>search link (open and pick the right page)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
         <is>
           <t>job link unknown</t>
         </is>
